--- a/services_forms/020_proof_of_service_form--services_forms.xlsx
+++ b/services_forms/020_proof_of_service_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'party_a'}</t>
+          <t>party_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'party_a'}</t>
+          <t>party a</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'party_b',_'label':_'party_b'}</t>
+          <t>party_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'party_b', 'label': 'party_b'}</t>
+          <t>party b</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'party_c',_'label':_'party_c'}</t>
+          <t>party_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'party_c', 'label': 'party_c'}</t>
+          <t>party c</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'party_d',_'label':_'party_d'}</t>
+          <t>party_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'party_d', 'label': 'party_d'}</t>
+          <t>party d</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'personal_service',_'label':_'personal_service'}</t>
+          <t>personal_service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'personal_service', 'label': 'Personal Service'}</t>
+          <t>Personal Service</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'certified_mail',_'label':_'certified_mail'}</t>
+          <t>certified_mail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'certified_mail', 'label': 'Certified Mail'}</t>
+          <t>Certified Mail</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fax',_'label':_'fax'}</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'fax', 'label': 'Fax'}</t>
+          <t>Fax</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'mail_box',_'label':_'mail_box'}</t>
+          <t>mail_box</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'mail_box', 'label': 'Mail Box'}</t>
+          <t>Mail Box</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
